--- a/output/pdf_financials_xlsx/BDGI.xlsx
+++ b/output/pdf_financials_xlsx/BDGI.xlsx
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>19.152</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>24.991</v>
@@ -1857,10 +1857,10 @@
         <v>0.008513</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.014617</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004768</v>
       </c>
     </row>
     <row r="35">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>19.152</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>24.991</v>
@@ -1937,10 +1937,10 @@
         <v>0.008513</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.014617</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004768</v>
       </c>
     </row>
     <row r="37">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>26.405</v>
+        <v>7.253</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>12.22</v>
@@ -2417,10 +2417,10 @@
         <v>0.019662</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.028495</v>
+        <v>0.013878</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.027071</v>
+        <v>0.022303</v>
       </c>
     </row>
     <row r="49">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/BDGI.xlsx
+++ b/output/pdf_financials_xlsx/BDGI.xlsx
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>1.276</v>
+        <v>34.887</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1.276</v>
+        <v>43.642</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>43.425</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>45.458</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>48.996</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>47.131</v>
+        <v>90.556</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>71.625</v>
+        <v>117.083</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>11.66025897942118</v>
+        <v>22.40364966031835</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.41703837297306</v>
+        <v>23.5670520603533</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -4469,16 +4469,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>34.887</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>43.642</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>43.425</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>45.458</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>48.996</v>
@@ -15463,7 +15463,11 @@
           <t>Additions to intangible asset 8</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -18243,7 +18247,11 @@
           <t>Additions to intangible asset 9</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20035,7 +20043,11 @@
           <t>Additions to intangible asset 10</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -22421,7 +22433,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -23758,7 +23774,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -24947,7 +24967,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -25018,7 +25042,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E275" s="5" t="n">
@@ -26643,7 +26667,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E298" s="5" t="n">
         <v>33.611</v>
       </c>
@@ -33027,7 +33055,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -34038,7 +34070,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -35169,7 +35201,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E424" s="5" t="n">
         <v>33.611</v>
       </c>
@@ -35236,7 +35272,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E425" s="5" t="n">

--- a/output/pdf_financials_xlsx/BDGI.xlsx
+++ b/output/pdf_financials_xlsx/BDGI.xlsx
@@ -1034,10 +1034,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H16" s="3" t="n">
+        <v>-0.011272</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.022883</v>
@@ -1248,10 +1246,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H20" s="3" t="n">
+        <v>-0.008737</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.01829</v>
@@ -1378,10 +1374,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>-0.008737</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.01829</v>
@@ -1508,10 +1502,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H26" s="3" t="n">
+        <v>0.034948</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.034509</v>
@@ -1558,10 +1550,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H27" s="3" t="n">
+        <v>-0.011272</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.022883</v>
@@ -1648,10 +1638,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H29" s="3" t="n">
+        <v>0.045853</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.082467</v>
@@ -1698,10 +1686,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H30" s="3" t="n">
+        <v>10.10178229164372</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>14.44731365142989</v>
@@ -1748,10 +1734,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H31" s="3" t="n">
+        <v>-22.48935415188077</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>20.07166892452913</v>
@@ -1798,10 +1782,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H32" s="3" t="n">
+        <v>-1.924830913617237</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>3.204207339719557</v>
@@ -2852,10 +2834,10 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>15.511</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>9.106</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>7.485</v>
@@ -2932,10 +2914,10 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0</v>
+        <v>15.511</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0</v>
+        <v>9.106</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0</v>
@@ -3172,37 +3154,37 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>8.468</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>11.519</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>16.616</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>18.523</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>32.294</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>37.287</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>53.19</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.051942</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.045913</v>
       </c>
     </row>
     <row r="68">
@@ -3212,37 +3194,37 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>30.44</v>
+        <v>38.908</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>30.765</v>
+        <v>40.632</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>28.999</v>
+        <v>40.518</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>39.312</v>
+        <v>55.928</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>54.453</v>
+        <v>72.976</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>67.357</v>
+        <v>99.651</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.04007</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.068831</v>
+        <v>37.355831</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.090019</v>
+        <v>53.280019</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.103225</v>
+        <v>0.155167</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.0949</v>
+        <v>0.140813</v>
       </c>
     </row>
     <row r="69">
@@ -3492,19 +3474,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>19.421</v>
+        <v>10.953</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>9.494</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>14.811</v>
+        <v>3.292</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>15.396</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>27.211</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -3519,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.041316</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.066208</v>
+        <v>0.020295</v>
       </c>
     </row>
     <row r="76">
@@ -4444,10 +4426,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" s="3" t="n">
+        <v>-0.008737</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>0.01829</v>
@@ -4752,13 +4732,13 @@
         <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>6.904</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.679</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0</v>
@@ -4773,13 +4753,13 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>-0.00722</v>
+        <v>0.010943</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>-0.011028</v>
+        <v>0.000283</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>-0.016095</v>
+        <v>0.025859</v>
       </c>
     </row>
     <row r="108">
@@ -5336,10 +5316,10 @@
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.006078</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.012744</v>
       </c>
     </row>
     <row r="122">
@@ -13791,7 +13771,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -14635,7 +14615,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -15810,7 +15794,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -17013,7 +17001,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19272,7 +19264,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -20607,7 +20603,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -22506,7 +22506,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -24123,7 +24127,11 @@
           <t>Share-based plan expense</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -25533,7 +25541,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -28726,7 +28738,11 @@
           <t>Deferred income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -31591,7 +31607,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -31725,7 +31745,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -33658,7 +33682,11 @@
           <t>Deferred income tax (recovery) expense 11</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
